--- a/research/traditional_assets/database/data/colombia/colombia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09520000000000001</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="E2">
-        <v>0.349</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
-        <v>0.3389880952380952</v>
+        <v>0.3282651072124756</v>
       </c>
       <c r="H2">
-        <v>0.2897321428571428</v>
+        <v>0.2923976608187135</v>
       </c>
       <c r="I2">
-        <v>0.2352678571428571</v>
+        <v>0.2846003898635477</v>
       </c>
       <c r="J2">
-        <v>0.1819595909163853</v>
+        <v>0.2011695906432748</v>
       </c>
       <c r="K2">
-        <v>35.82</v>
+        <v>9.52</v>
       </c>
       <c r="L2">
-        <v>0.5330357142857143</v>
+        <v>0.1855750487329435</v>
       </c>
       <c r="M2">
-        <v>20.62</v>
+        <v>7.91</v>
       </c>
       <c r="N2">
-        <v>0.119536231884058</v>
+        <v>0.09081515499425948</v>
       </c>
       <c r="O2">
-        <v>0.5756560580681184</v>
+        <v>0.8308823529411765</v>
       </c>
       <c r="P2">
-        <v>20.62</v>
+        <v>7.91</v>
       </c>
       <c r="Q2">
-        <v>0.119536231884058</v>
+        <v>0.09081515499425948</v>
       </c>
       <c r="R2">
-        <v>0.5756560580681184</v>
+        <v>0.8308823529411765</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.61</v>
+        <v>14.6</v>
       </c>
       <c r="V2">
-        <v>0.06730434782608695</v>
+        <v>0.1676234213547647</v>
       </c>
       <c r="W2">
-        <v>0.2053849902534113</v>
+        <v>0.06246719160104986</v>
       </c>
       <c r="X2">
-        <v>0.02681481042561934</v>
+        <v>0.05586859510734557</v>
       </c>
       <c r="Y2">
-        <v>0.1785701798277919</v>
+        <v>0.006598596493704291</v>
       </c>
       <c r="Z2">
-        <v>0.5261756737710822</v>
+        <v>0.4380496968661941</v>
       </c>
       <c r="AA2">
-        <v>0.1264396072188594</v>
+        <v>0.08812227819998292</v>
       </c>
       <c r="AB2">
-        <v>0.02683272479540234</v>
+        <v>0.05374792572951774</v>
       </c>
       <c r="AC2">
-        <v>0.09960688242345705</v>
+        <v>0.03437435247046518</v>
       </c>
       <c r="AD2">
-        <v>6.502</v>
+        <v>23.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.502</v>
+        <v>23.5</v>
       </c>
       <c r="AG2">
-        <v>-5.108</v>
+        <v>8.9</v>
       </c>
       <c r="AH2">
-        <v>0.03632361649590507</v>
+        <v>0.2124773960216998</v>
       </c>
       <c r="AI2">
-        <v>0.03320701525009959</v>
+        <v>0.1442602823818293</v>
       </c>
       <c r="AJ2">
-        <v>-0.03051519785891799</v>
+        <v>0.09270833333333334</v>
       </c>
       <c r="AK2">
-        <v>-0.0277319318971508</v>
+        <v>0.06001348617666891</v>
       </c>
       <c r="AL2">
-        <v>0.8160000000000001</v>
+        <v>0.239</v>
       </c>
       <c r="AM2">
-        <v>0.295</v>
+        <v>0.239</v>
       </c>
       <c r="AN2">
-        <v>0.396947496947497</v>
+        <v>1.424242424242424</v>
       </c>
       <c r="AO2">
-        <v>19.375</v>
+        <v>61.08786610878661</v>
       </c>
       <c r="AP2">
-        <v>-0.3118437118437118</v>
+        <v>0.5393939393939394</v>
       </c>
       <c r="AQ2">
-        <v>53.59322033898304</v>
+        <v>61.08786610878661</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BMC Bolsa Mercantil de Colombia S.A. (BVC:BMC)</t>
+          <t>Bolsa de Valores de Colombia S.A. (BVC:BVC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.132</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="E3">
-        <v>0.28</v>
+        <v>0.175</v>
       </c>
       <c r="G3">
-        <v>0.3622516556291391</v>
+        <v>0.3282651072124756</v>
       </c>
       <c r="H3">
-        <v>0.3622516556291391</v>
+        <v>0.2923976608187135</v>
       </c>
       <c r="I3">
-        <v>0.3119205298013245</v>
+        <v>0.2846003898635477</v>
       </c>
       <c r="J3">
-        <v>0.235017046122497</v>
+        <v>0.2011695906432748</v>
       </c>
       <c r="K3">
-        <v>3.82</v>
+        <v>9.52</v>
       </c>
       <c r="L3">
-        <v>0.2529801324503311</v>
+        <v>0.1855750487329435</v>
       </c>
       <c r="M3">
-        <v>3.52</v>
+        <v>7.91</v>
       </c>
       <c r="N3">
-        <v>0.1485232067510548</v>
+        <v>0.09081515499425948</v>
       </c>
       <c r="O3">
-        <v>0.9214659685863875</v>
+        <v>0.8308823529411765</v>
       </c>
       <c r="P3">
-        <v>3.52</v>
+        <v>7.91</v>
       </c>
       <c r="Q3">
-        <v>0.1485232067510548</v>
+        <v>0.09081515499425948</v>
       </c>
       <c r="R3">
-        <v>0.9214659685863875</v>
+        <v>0.8308823529411765</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,207 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.41</v>
+        <v>14.6</v>
       </c>
       <c r="V3">
-        <v>0.05949367088607595</v>
+        <v>0.1676234213547647</v>
       </c>
       <c r="W3">
-        <v>0.1768518518518518</v>
+        <v>0.06246719160104986</v>
       </c>
       <c r="X3">
-        <v>0.02665892068079052</v>
+        <v>0.05586859510734557</v>
       </c>
       <c r="Y3">
-        <v>0.1501929311710613</v>
+        <v>0.006598596493704291</v>
       </c>
       <c r="Z3">
-        <v>0.7254732391659459</v>
+        <v>0.4380496968661941</v>
       </c>
       <c r="AA3">
-        <v>0.1704985777097004</v>
+        <v>0.08812227819998292</v>
       </c>
       <c r="AB3">
-        <v>0.02668178967065758</v>
+        <v>0.05374792572951774</v>
       </c>
       <c r="AC3">
-        <v>0.1438167880390428</v>
+        <v>0.03437435247046518</v>
       </c>
       <c r="AD3">
-        <v>0.092</v>
+        <v>23.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.092</v>
+        <v>23.5</v>
       </c>
       <c r="AG3">
-        <v>-1.318</v>
+        <v>8.9</v>
       </c>
       <c r="AH3">
-        <v>0.003866845998655011</v>
+        <v>0.2124773960216998</v>
       </c>
       <c r="AI3">
-        <v>0.004221732745961822</v>
+        <v>0.1442602823818293</v>
       </c>
       <c r="AJ3">
-        <v>-0.05888660530783665</v>
+        <v>0.09270833333333334</v>
       </c>
       <c r="AK3">
-        <v>-0.06466490040231576</v>
+        <v>0.06001348617666891</v>
       </c>
       <c r="AL3">
-        <v>0.008999999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="AM3">
-        <v>-0.512</v>
+        <v>0.239</v>
       </c>
       <c r="AN3">
-        <v>0.01924686192468619</v>
+        <v>1.424242424242424</v>
       </c>
       <c r="AO3">
-        <v>523.3333333333334</v>
+        <v>61.08786610878661</v>
       </c>
       <c r="AP3">
-        <v>-0.2757322175732217</v>
+        <v>0.5393939393939394</v>
       </c>
       <c r="AQ3">
-        <v>-9.19921875</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bolsa de Valores de Colombia S.A. (BVC:BVC)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0584</v>
-      </c>
-      <c r="E4">
-        <v>0.418</v>
-      </c>
-      <c r="G4">
-        <v>0.3322456813819578</v>
-      </c>
-      <c r="H4">
-        <v>0.2687140115163148</v>
-      </c>
-      <c r="I4">
-        <v>0.2130518234165067</v>
-      </c>
-      <c r="J4">
-        <v>0.1690305195052815</v>
-      </c>
-      <c r="K4">
-        <v>32</v>
-      </c>
-      <c r="L4">
-        <v>0.6142034548944337</v>
-      </c>
-      <c r="M4">
-        <v>17.1</v>
-      </c>
-      <c r="N4">
-        <v>0.1149193548387097</v>
-      </c>
-      <c r="O4">
-        <v>0.534375</v>
-      </c>
-      <c r="P4">
-        <v>17.1</v>
-      </c>
-      <c r="Q4">
-        <v>0.1149193548387097</v>
-      </c>
-      <c r="R4">
-        <v>0.534375</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>10.2</v>
-      </c>
-      <c r="V4">
-        <v>0.06854838709677419</v>
-      </c>
-      <c r="W4">
-        <v>0.2339181286549707</v>
-      </c>
-      <c r="X4">
-        <v>0.02697070017044817</v>
-      </c>
-      <c r="Y4">
-        <v>0.2069474284845226</v>
-      </c>
-      <c r="Z4">
-        <v>0.4873713751169317</v>
-      </c>
-      <c r="AA4">
-        <v>0.08238063672801839</v>
-      </c>
-      <c r="AB4">
-        <v>0.0269836599201471</v>
-      </c>
-      <c r="AC4">
-        <v>0.05539697680787128</v>
-      </c>
-      <c r="AD4">
-        <v>6.41</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>6.41</v>
-      </c>
-      <c r="AG4">
-        <v>-3.789999999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.04129888538109658</v>
-      </c>
-      <c r="AI4">
-        <v>0.03683696339290846</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.0261361285428591</v>
-      </c>
-      <c r="AK4">
-        <v>-0.02313656064953299</v>
-      </c>
-      <c r="AL4">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="AM4">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="AN4">
-        <v>0.5525862068965518</v>
-      </c>
-      <c r="AO4">
-        <v>13.7546468401487</v>
-      </c>
-      <c r="AP4">
-        <v>-0.3267241379310344</v>
-      </c>
-      <c r="AQ4">
-        <v>13.7546468401487</v>
+        <v>61.08786610878661</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/colombia/colombia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08039999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="E2">
-        <v>0.175</v>
+        <v>-0.224</v>
       </c>
       <c r="G2">
-        <v>0.3282651072124756</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="H2">
-        <v>0.2923976608187135</v>
+        <v>0.2027777777777778</v>
       </c>
       <c r="I2">
-        <v>0.2846003898635477</v>
+        <v>0.3027777777777778</v>
       </c>
       <c r="J2">
-        <v>0.2011695906432748</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="K2">
-        <v>9.52</v>
+        <v>8.5</v>
       </c>
       <c r="L2">
-        <v>0.1855750487329435</v>
+        <v>0.1180555555555556</v>
       </c>
       <c r="M2">
-        <v>7.91</v>
+        <v>12.5</v>
       </c>
       <c r="N2">
-        <v>0.09081515499425948</v>
+        <v>0.06856829402084476</v>
       </c>
       <c r="O2">
-        <v>0.8308823529411765</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="P2">
-        <v>7.91</v>
+        <v>12.5</v>
       </c>
       <c r="Q2">
-        <v>0.09081515499425948</v>
+        <v>0.06856829402084476</v>
       </c>
       <c r="R2">
-        <v>0.8308823529411765</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.6</v>
+        <v>21.7</v>
       </c>
       <c r="V2">
-        <v>0.1676234213547647</v>
+        <v>0.1190345584201865</v>
       </c>
       <c r="W2">
-        <v>0.06246719160104986</v>
+        <v>0.06640625</v>
       </c>
       <c r="X2">
-        <v>0.05586859510734557</v>
+        <v>0.05722431346615746</v>
       </c>
       <c r="Y2">
-        <v>0.006598596493704291</v>
+        <v>0.009181936533842541</v>
       </c>
       <c r="Z2">
-        <v>0.4380496968661941</v>
+        <v>0.6492335437330928</v>
       </c>
       <c r="AA2">
-        <v>0.08812227819998292</v>
+        <v>0.09828674481514878</v>
       </c>
       <c r="AB2">
-        <v>0.05374792572951774</v>
+        <v>0.05635204472991259</v>
       </c>
       <c r="AC2">
-        <v>0.03437435247046518</v>
+        <v>0.04193470008523618</v>
       </c>
       <c r="AD2">
-        <v>23.5</v>
+        <v>11.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23.5</v>
+        <v>11.7</v>
       </c>
       <c r="AG2">
-        <v>8.9</v>
+        <v>-10</v>
       </c>
       <c r="AH2">
-        <v>0.2124773960216998</v>
+        <v>0.06030927835051546</v>
       </c>
       <c r="AI2">
-        <v>0.1442602823818293</v>
+        <v>0.07060953530476766</v>
       </c>
       <c r="AJ2">
-        <v>0.09270833333333334</v>
+        <v>-0.05803830528148578</v>
       </c>
       <c r="AK2">
-        <v>0.06001348617666891</v>
+        <v>-0.06944444444444445</v>
       </c>
       <c r="AL2">
-        <v>0.239</v>
+        <v>0.059</v>
       </c>
       <c r="AM2">
-        <v>0.239</v>
+        <v>0.059</v>
       </c>
       <c r="AN2">
-        <v>1.424242424242424</v>
+        <v>0.4936708860759493</v>
       </c>
       <c r="AO2">
-        <v>61.08786610878661</v>
+        <v>369.4915254237288</v>
       </c>
       <c r="AP2">
-        <v>0.5393939393939394</v>
+        <v>-0.4219409282700422</v>
       </c>
       <c r="AQ2">
-        <v>61.08786610878661</v>
+        <v>369.4915254237288</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08039999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="E3">
-        <v>0.175</v>
+        <v>-0.224</v>
       </c>
       <c r="G3">
-        <v>0.3282651072124756</v>
+        <v>0.2479166666666667</v>
       </c>
       <c r="H3">
-        <v>0.2923976608187135</v>
+        <v>0.2027777777777778</v>
       </c>
       <c r="I3">
-        <v>0.2846003898635477</v>
+        <v>0.3027777777777778</v>
       </c>
       <c r="J3">
-        <v>0.2011695906432748</v>
+        <v>0.1513888888888889</v>
       </c>
       <c r="K3">
-        <v>9.52</v>
+        <v>8.5</v>
       </c>
       <c r="L3">
-        <v>0.1855750487329435</v>
+        <v>0.1180555555555556</v>
       </c>
       <c r="M3">
-        <v>7.91</v>
+        <v>12.5</v>
       </c>
       <c r="N3">
-        <v>0.09081515499425948</v>
+        <v>0.06856829402084476</v>
       </c>
       <c r="O3">
-        <v>0.8308823529411765</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="P3">
-        <v>7.91</v>
+        <v>12.5</v>
       </c>
       <c r="Q3">
-        <v>0.09081515499425948</v>
+        <v>0.06856829402084476</v>
       </c>
       <c r="R3">
-        <v>0.8308823529411765</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.6</v>
+        <v>21.7</v>
       </c>
       <c r="V3">
-        <v>0.1676234213547647</v>
+        <v>0.1190345584201865</v>
       </c>
       <c r="W3">
-        <v>0.06246719160104986</v>
+        <v>0.06640625</v>
       </c>
       <c r="X3">
-        <v>0.05586859510734557</v>
+        <v>0.05722431346615746</v>
       </c>
       <c r="Y3">
-        <v>0.006598596493704291</v>
+        <v>0.009181936533842541</v>
       </c>
       <c r="Z3">
-        <v>0.4380496968661941</v>
+        <v>0.6492335437330928</v>
       </c>
       <c r="AA3">
-        <v>0.08812227819998292</v>
+        <v>0.09828674481514878</v>
       </c>
       <c r="AB3">
-        <v>0.05374792572951774</v>
+        <v>0.05635204472991259</v>
       </c>
       <c r="AC3">
-        <v>0.03437435247046518</v>
+        <v>0.04193470008523618</v>
       </c>
       <c r="AD3">
-        <v>23.5</v>
+        <v>11.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>23.5</v>
+        <v>11.7</v>
       </c>
       <c r="AG3">
-        <v>8.9</v>
+        <v>-10</v>
       </c>
       <c r="AH3">
-        <v>0.2124773960216998</v>
+        <v>0.06030927835051546</v>
       </c>
       <c r="AI3">
-        <v>0.1442602823818293</v>
+        <v>0.07060953530476766</v>
       </c>
       <c r="AJ3">
-        <v>0.09270833333333334</v>
+        <v>-0.05803830528148578</v>
       </c>
       <c r="AK3">
-        <v>0.06001348617666891</v>
+        <v>-0.06944444444444445</v>
       </c>
       <c r="AL3">
-        <v>0.239</v>
+        <v>0.059</v>
       </c>
       <c r="AM3">
-        <v>0.239</v>
+        <v>0.059</v>
       </c>
       <c r="AN3">
-        <v>1.424242424242424</v>
+        <v>0.4936708860759493</v>
       </c>
       <c r="AO3">
-        <v>61.08786610878661</v>
+        <v>369.4915254237288</v>
       </c>
       <c r="AP3">
-        <v>0.5393939393939394</v>
+        <v>-0.4219409282700422</v>
       </c>
       <c r="AQ3">
-        <v>61.08786610878661</v>
+        <v>369.4915254237288</v>
       </c>
     </row>
   </sheetData>
